--- a/metas.xlsx
+++ b/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/04 Abril/Liquidacióncvs - ensayo/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/04 Abril/Liquidacióncvs - VENTAS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="866" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D71A4081-4C97-480C-847E-4E46766B17EB}"/>
+  <xr:revisionPtr revIDLastSave="913" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3E81D42-4A75-45AD-91B5-EFE21D66D5B4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$126</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="36">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Abril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAN CRISTOBAL </t>
   </si>
 </sst>
 </file>
@@ -530,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -567,7 +570,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="2">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E2" s="2">
         <v>2800</v>
@@ -737,7 +740,7 @@
         <v>22</v>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2">
         <v>1350</v>
@@ -992,7 +995,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="2">
-        <v>1200</v>
+        <v>950</v>
       </c>
       <c r="E27" s="2">
         <v>1500</v>
@@ -1926,7 +1929,7 @@
       <c r="C82" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="2">
         <v>1500</v>
       </c>
       <c r="E82" s="2">
@@ -2182,7 +2185,7 @@
         <v>22</v>
       </c>
       <c r="D97" s="2">
-        <v>1500</v>
+        <v>682</v>
       </c>
       <c r="E97" s="2">
         <v>6000</v>
@@ -2431,16 +2434,16 @@
         <v>34</v>
       </c>
       <c r="B112" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D112">
-        <v>27700</v>
+      <c r="D112" s="2">
+        <v>1</v>
       </c>
       <c r="E112" s="2">
-        <v>53400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2448,16 +2451,16 @@
         <v>34</v>
       </c>
       <c r="B113" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D113" s="2">
-        <v>820</v>
+        <v>15</v>
       </c>
       <c r="E113" s="2">
-        <v>53400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -2465,16 +2468,16 @@
         <v>34</v>
       </c>
       <c r="B114" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D114" s="2">
-        <v>136</v>
+        <v>4</v>
       </c>
       <c r="E114" s="2">
-        <v>53400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2482,16 +2485,16 @@
         <v>34</v>
       </c>
       <c r="B115" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D115" s="2">
-        <v>1637</v>
+        <v>30</v>
       </c>
       <c r="E115" s="2">
-        <v>53400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -2499,16 +2502,16 @@
         <v>34</v>
       </c>
       <c r="B116" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D116" s="2">
-        <v>3085</v>
+        <v>70</v>
       </c>
       <c r="E116" s="2">
-        <v>53400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -2516,13 +2519,13 @@
         <v>34</v>
       </c>
       <c r="B117" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D117" s="2">
-        <v>1500</v>
+      <c r="D117">
+        <v>26532</v>
       </c>
       <c r="E117" s="2">
         <v>53400</v>
@@ -2533,7 +2536,7 @@
         <v>34</v>
       </c>
       <c r="B118" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>27</v>
@@ -2550,7 +2553,7 @@
         <v>34</v>
       </c>
       <c r="B119" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>28</v>
@@ -2567,7 +2570,7 @@
         <v>34</v>
       </c>
       <c r="B120" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>29</v>
@@ -2584,7 +2587,7 @@
         <v>34</v>
       </c>
       <c r="B121" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>30</v>
@@ -2596,8 +2599,93 @@
         <v>53400</v>
       </c>
     </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>34</v>
+      </c>
+      <c r="B122" t="s">
+        <v>33</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D122" s="2">
+        <v>1</v>
+      </c>
+      <c r="E122" s="2">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>34</v>
+      </c>
+      <c r="B123" t="s">
+        <v>33</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D123" s="2">
+        <v>820</v>
+      </c>
+      <c r="E123" s="2">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>34</v>
+      </c>
+      <c r="B124" t="s">
+        <v>33</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" s="2">
+        <v>136</v>
+      </c>
+      <c r="E124" s="2">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>34</v>
+      </c>
+      <c r="B125" t="s">
+        <v>33</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D125" s="2">
+        <v>1637</v>
+      </c>
+      <c r="E125" s="2">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>34</v>
+      </c>
+      <c r="B126" t="s">
+        <v>33</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D126" s="2">
+        <v>3085</v>
+      </c>
+      <c r="E126" s="2">
+        <v>53400</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E121" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:E126" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>